--- a/content/kontent-plan-dzen-hant.xlsx
+++ b/content/kontent-plan-dzen-hant.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Лестница Ханта" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Контент-план" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Календарь · Август" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -120,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -172,6 +173,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2132,4 +2139,608 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Календарь публикаций · Август 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ритм: 3 поста в неделю — понедельник / среда / пятница. Ступени Ханта и форматы чередуются: охватные темы (ст. 0–1) двигают алгоритм, ст. 2–3 ведут к продуктам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>День</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ст.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Тема / заголовок</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Рубрика</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Формат</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Роль в стратегии</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>03.08</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Почему Китай называют Поднебесной</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Культура</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Лонгрид</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Мощный охватный старт (спрос 45k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>05.08</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Как поздороваться по-китайски: 你好 и не только</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Практика</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Пост</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Лёгкий вовлекающий пост</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>07.08</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Топ-50 базовых глаголов с примерами</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Язык</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Лонгрид + картинки</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>готово</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Экспертность, быстрый выпуск</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>10.08</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Сколько на самом деле «китайских языков»: диалекты</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Культура</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Лонгрид</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Охват (спрос 21k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>12.08</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Тоны в китайском: почему «ма» — это разные слова</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Язык</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Пост + инфографика</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Польза + визуал</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>14.08</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>HSK: что за экзамен и с чего начать</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>HSK</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Лонгрид</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>есть в блоге</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Ввод в воронку (спрос 40k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17.08</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Средняя зарплата в Китае: сколько и за что платят</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Жизнь в Китае</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Лонгрид</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Охват (спрос 21k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Считаем по-китайски: цифры от 0 до 10</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Практика</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Пост + инфографика</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Практическая польза</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21.08</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Можно ли выучить китайский самостоятельно</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Как учить</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Лонгрид</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Экспертность, удержание</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>24.08</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Социальный рейтинг в Китае: как он устроен</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Жизнь в Китае</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Лонгрид</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Охват (спрос 11k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>26.08</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Китайский для детей: во сколько начинать</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Учёба</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Лонгрид</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>есть в блоге</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Воронка (родители, спрос 27k)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>28.08</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Разбираем реальный пробный тест HSK 1</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>HSK</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Тест / разбор</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>есть в блоге</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Доказательство экспертизы</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>31.08</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Китайские пословицы и идиомы, которые стоит знать</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Культура</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Лонгрид + карточки</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Охватный финал месяца (спрос 8k)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>